--- a/history_matching/examples/DTK/Data/CountryData.xlsx
+++ b/history_matching/examples/DTK/Data/CountryData.xlsx
@@ -150,18 +150,18 @@
         <v>0.1</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
